--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>80.34067078359503</v>
+        <v>13.05535900233419</v>
       </c>
       <c r="D2" t="n">
-        <v>32.76414275065083</v>
+        <v>5.324173196980761</v>
       </c>
       <c r="E2" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F2" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.22024471030595</v>
+        <v>11.57328976542472</v>
       </c>
       <c r="D3" t="n">
-        <v>24.58761438712589</v>
+        <v>3.995487337907957</v>
       </c>
       <c r="E3" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F3" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.60991979851446</v>
+        <v>1.886611967258599</v>
       </c>
       <c r="D4" t="n">
-        <v>11.37734203363234</v>
+        <v>1.848818080465255</v>
       </c>
       <c r="E4" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F4" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.5055048042469</v>
+        <v>7.232144530690122</v>
       </c>
       <c r="D5" t="n">
-        <v>29.98277100082401</v>
+        <v>4.872200287633901</v>
       </c>
       <c r="E5" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F5" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.80771712157776</v>
+        <v>4.843754032256386</v>
       </c>
       <c r="D6" t="n">
-        <v>30.9028588488531</v>
+        <v>5.021714562938629</v>
       </c>
       <c r="E6" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F6" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.89196774815242</v>
+        <v>3.557444759074769</v>
       </c>
       <c r="D7" t="n">
-        <v>23.08541911091479</v>
+        <v>3.751380605523654</v>
       </c>
       <c r="E7" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F7" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.64835695596386</v>
+        <v>5.955358005344128</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46457509813727</v>
+        <v>5.925493453447306</v>
       </c>
       <c r="E8" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F8" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.95927594539284</v>
+        <v>3.568382341126337</v>
       </c>
       <c r="D9" t="n">
-        <v>45.4020867142605</v>
+        <v>7.377839091067331</v>
       </c>
       <c r="E9" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F9" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.80747059789785</v>
+        <v>2.5687139721584</v>
       </c>
       <c r="D10" t="n">
-        <v>45.46782335304702</v>
+        <v>7.388521294870141</v>
       </c>
       <c r="E10" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F10" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.851027968104097</v>
+        <v>1.113292044816916</v>
       </c>
       <c r="D11" t="n">
-        <v>43.51490521034759</v>
+        <v>7.071172096681484</v>
       </c>
       <c r="E11" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F11" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.009868012026379</v>
+        <v>1.301603551954287</v>
       </c>
       <c r="D12" t="n">
-        <v>7.269944860948398</v>
+        <v>1.181366039904115</v>
       </c>
       <c r="E12" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F12" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.64377002658678</v>
+        <v>4.167112629320353</v>
       </c>
       <c r="D13" t="n">
-        <v>14.18770778644547</v>
+        <v>2.305502515297388</v>
       </c>
       <c r="E13" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F13" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.84776036512276</v>
+        <v>4.525261059332448</v>
       </c>
       <c r="D14" t="n">
-        <v>28.39966112921409</v>
+        <v>4.614944933497291</v>
       </c>
       <c r="E14" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F14" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.50328765862038</v>
+        <v>2.844284244525811</v>
       </c>
       <c r="D15" t="n">
-        <v>17.50125850674189</v>
+        <v>2.843954507345558</v>
       </c>
       <c r="E15" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F15" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>45.62104521320332</v>
+        <v>7.413419847145539</v>
       </c>
       <c r="D16" t="n">
-        <v>44.92596961266612</v>
+        <v>7.300470062058244</v>
       </c>
       <c r="E16" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F16" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>12.25648944506493</v>
+        <v>1.991679534823052</v>
       </c>
       <c r="D17" t="n">
-        <v>44.03788697602567</v>
+        <v>7.156156633604171</v>
       </c>
       <c r="E17" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F17" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.07786634979163</v>
+        <v>5.700153281841141</v>
       </c>
       <c r="D18" t="n">
-        <v>35.80298401512638</v>
+        <v>5.817984902458036</v>
       </c>
       <c r="E18" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F18" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>16.60235526013266</v>
+        <v>2.697882729771558</v>
       </c>
       <c r="D19" t="n">
-        <v>70.05717111915278</v>
+        <v>11.38429030686233</v>
       </c>
       <c r="E19" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F19" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.23441630194445</v>
+        <v>3.775592649065973</v>
       </c>
       <c r="D20" t="n">
-        <v>76.61365832024691</v>
+        <v>12.44971947704012</v>
       </c>
       <c r="E20" t="n">
-        <v>19.40000796893683</v>
+        <v>3.152501294952234</v>
       </c>
       <c r="F20" t="n">
-        <v>17.53320532137012</v>
+        <v>2.849145864722644</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
